--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5281-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5281-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9CCBCDD-2294-4674-A8F7-7594BADEA9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20FC6EF9-0FEC-4E24-95F7-80B6014E52E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E9E6505C-C63E-412B-9D7F-9A55F16A9CA1}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{882EBAC0-3E54-4128-8E5A-6C21B3301B9F}"/>
   </bookViews>
   <sheets>
     <sheet name="5281-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1466,30 +1466,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EF8078B-E41E-4A76-B28C-55AE7FDF461A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F4A7A3-4132-4B38-A361-08A61C17DA6A}">
   <dimension ref="A1:X37"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1679,7 +1679,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2023</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2022</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2021</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2020</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2019</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2018</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2017</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2016</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2015</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2014</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35" t="s">
         <v>43</v>
       </c>
